--- a/testData/Login_data.xlsx
+++ b/testData/Login_data.xlsx
@@ -2,18 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/36cb6faa52e30403/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PANCHALINGAM\Java workspace\E-Commerce\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71568343-817F-4B53-BD5C-6936469DFB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C05F16-70AE-4B9C-BDD4-FFC03481BF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{19834151-793F-4DC3-B944-073113AF1BCB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{19834151-793F-4DC3-B944-073113AF1BCB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="testData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>username</t>
   </si>
@@ -81,6 +82,30 @@
   </si>
   <si>
     <t>Virat@18</t>
+  </si>
+  <si>
+    <t>TestData</t>
+  </si>
+  <si>
+    <t>Desktops</t>
+  </si>
+  <si>
+    <t>Mac</t>
+  </si>
+  <si>
+    <t>iMac</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>execute</t>
   </si>
 </sst>
 </file>
@@ -104,7 +129,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -114,6 +139,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -131,10 +168,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -557,4 +596,59 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6545EF97-8E68-46D7-A5DD-FDFD9860DCC3}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="D1" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>